--- a/survey_templates/028_internal_communications_quality_survey--survey_templates.xlsx
+++ b/survey_templates/028_internal_communications_quality_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>communication_effectiveness</t>
+          <t>Communication Effectiveness</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>communication_frequency</t>
+          <t>Communication Frequency</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>engagement</t>
+          <t>preferred_communication_channels</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>engagement</t>
+          <t>Preferred Communication Channels</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>communication_channels</t>
+          <t>communication_strategy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>communication_channels</t>
+          <t>Communication Strategy</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>preferred_communication_channels</t>
+          <t>communication_level</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>preferred_communication_channels</t>
+          <t>Communication Level</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>communication_style</t>
+          <t>communication_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>communication_style</t>
+          <t>Communication Time</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>response_rate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>Response Rate</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>response_time</t>
+          <t>communication_content</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>response_time</t>
+          <t>Communication Content</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>response_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>Response Time</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>response_rate</t>
+          <t>follow_up</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>response_rate</t>
+          <t>Follow-up</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>communication_quality</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>Communication Quality</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>feedback_frequentcy</t>
+          <t>communication_channels_used</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>feedback_frequency</t>
+          <t>Communication Channels Used</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>communication_strategy</t>
+          <t>communication_frequency_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>communication_strategy</t>
+          <t>Communication Frequency 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>communication_channels_used</t>
+          <t>communication_level_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>communication_channels_used</t>
+          <t>Communication Level 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,223 +865,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>communication_content</t>
+          <t>time_spend</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>communication_content</t>
+          <t>Time Spend</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>communication_level</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>communication_level</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>time_spend</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>time_spend</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>communication_quality</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>communication_quality</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>response_rate</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>response_rate</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>communication_frequency</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>communication_frequency</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>communication_channels_used</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>communication_channels_used</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>communication_level</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>communication_level</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>communication_time</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>communication_time</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>communication_effectiveness</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>communication_effectiveness</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1126,34 +919,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>communication_frequency_choices</t>
+          <t>communication_effectiveness_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>formal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Formal</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>communication_frequency_choices</t>
+          <t>communication_effectiveness_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>informal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Informal</t>
         </is>
       </c>
     </row>
@@ -1165,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1182,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1199,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>semi-annually</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Semi-Annually</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1216,114 +1009,114 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>annually</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Annually</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>communication_channels_choices</t>
+          <t>communication_frequency_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>semi-annually</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Semi-Annually</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>communication_channels_choices</t>
+          <t>communication_frequency_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>communication_channels_choices</t>
+          <t>preferred_communication_channels_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>team_meetings</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Team meetings</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>communication_channels_choices</t>
+          <t>preferred_communication_channels_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>text_message</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Text message</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>communication_channels_choices</t>
+          <t>preferred_communication_channels_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>team_meetings</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Social media</t>
+          <t>Team meetings</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>communication_channels_choices</t>
+          <t>preferred_communication_channels_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>company_intranet</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Company intranet</t>
+          <t>Text message</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -1352,165 +1145,165 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>company_intranet</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Company intranet</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>preferred_communication_channels_choices</t>
+          <t>communication_strategy_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>team_meetings</t>
+          <t>formal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Team meetings</t>
+          <t>Formal</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>preferred_communication_channels_choices</t>
+          <t>communication_strategy_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>text_message</t>
+          <t>informal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Text message</t>
+          <t>Informal</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>preferred_communication_channels_choices</t>
+          <t>communication_level_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>formal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Social media</t>
+          <t>Formal</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>preferred_communication_channels_choices</t>
+          <t>communication_level_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>company_intranet</t>
+          <t>informal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Company intranet</t>
+          <t>Informal</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>communication_style_choices</t>
+          <t>communication_content_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>formal</t>
+          <t>company_news</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Formal</t>
+          <t>Company news</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>communication_style_choices</t>
+          <t>communication_content_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>informal</t>
+          <t>team_news</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Informal</t>
+          <t>Team news</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>time_management_choices</t>
+          <t>communication_content_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>on_time</t>
+          <t>manager_news</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>On time</t>
+          <t>Manager news</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>time_management_choices</t>
+          <t>communication_content_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>employee_newsletters</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Late</t>
+          <t>Employee newsletters</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>time_management_choices</t>
+          <t>communication_content_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>as_needed</t>
+          <t>internal_news_feed</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>Internal news feed</t>
         </is>
       </c>
     </row>
@@ -1568,731 +1361,306 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>communication_channels_used_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>communication_channels_used_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>communication_channels_used_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>as_needed</t>
+          <t>team_meetings</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>Team meetings</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>feedback_frequentcy_choices</t>
+          <t>communication_channels_used_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Text message</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>feedback_frequentcy_choices</t>
+          <t>communication_channels_used_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>feedback_frequentcy_choices</t>
+          <t>communication_channels_used_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>company_intranet</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Company intranet</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>feedback_frequentcy_choices</t>
+          <t>communication_frequency_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>feedback_frequentcy_choices</t>
+          <t>communication_frequency_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>semi-annually</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Semi-Annually</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>feedback_frequentcy_choices</t>
+          <t>communication_frequency_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>annually</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Annually</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>communication_strategy_choices</t>
+          <t>communication_frequency_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>formal</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Formal</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>communication_strategy_choices</t>
+          <t>communication_frequency_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>informal</t>
+          <t>semi-annually</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Informal</t>
+          <t>Semi-Annually</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>communication_channels_used_choices</t>
+          <t>communication_frequency_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>communication_channels_used_choices</t>
+          <t>communication_level_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>formal</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Formal</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>communication_channels_used_choices</t>
+          <t>communication_level_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>team_meetings</t>
+          <t>informal</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Team meetings</t>
+          <t>Informal</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>communication_channels_used_choices</t>
+          <t>time_spend_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>text_message</t>
+          <t>less_than_1_hour</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Text message</t>
+          <t>Less than 1 hour</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>communication_channels_used_choices</t>
+          <t>time_spend_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>1-2_hours</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Social media</t>
+          <t>1-2 hours</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>communication_channels_used_choices</t>
+          <t>time_spend_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>company_intranet</t>
+          <t>2-4_hours</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Company intranet</t>
+          <t>2-4 hours</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>communication_content_choices</t>
+          <t>time_spend_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>company_news</t>
+          <t>more_than_4_hours</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Company news</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>communication_content_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>team_news</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Team news</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>communication_content_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>manager_news</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Manager news</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>communication_content_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>employee_newsletters</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Employee newsletters</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>communication_content_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>internal_news_feed</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Internal news feed</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>communication_content_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>personal_messages</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Personal messages</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>communication_level_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>formal</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>communication_level_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>informal</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>time_spend_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>less_than_1_hour</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Less than 1 hour</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>time_spend_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>1-2_hours</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1-2 hours</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>time_spend_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2-4_hours</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2-4 hours</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>time_spend_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>more_than_4_hours</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
           <t>More than 4 hours</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>communication_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>communication_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>communication_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>communication_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>communication_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>semi-annually</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Semi-Annually</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>communication_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>annually</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Annually</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>communication_channels_used_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>communication_channels_used_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>communication_channels_used_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>team_meetings</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Team meetings</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>communication_channels_used_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>text_message</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Text message</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>communication_channels_used_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>social_media</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Social media</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>communication_channels_used_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>company_intranet</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Company intranet</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>communication_level_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>formal</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>communication_level_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>informal</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Informal</t>
         </is>
       </c>
     </row>
